--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T10:56:37+00:00</t>
+    <t>2025-01-17T11:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T11:40:58+00:00</t>
+    <t>2025-01-21T12:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-21T12:24:15+00:00</t>
+    <t>2025-01-23T11:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:46:49+00:00</t>
+    <t>2025-01-24T11:26:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,13 +653,10 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-ips-laboratory-pathology-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -872,6 +869,13 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t xml:space="preserve">obs-7
 </t>
   </si>
@@ -888,6 +892,12 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -904,9 +914,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -939,10 +946,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-observationinterpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -993,6 +997,9 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1373,6 +1380,12 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
@@ -1403,6 +1416,12 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -1713,12 +1732,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1741,7 +1760,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="87.55859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3638,11 +3657,9 @@
       <c r="X16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3675,30 +3692,30 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3721,19 +3738,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3782,7 +3799,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3797,19 +3814,19 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3817,10 +3834,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3843,16 +3860,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3902,7 +3919,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3923,13 +3940,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3937,14 +3954,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3963,19 +3980,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4024,7 +4041,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4039,19 +4056,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4059,14 +4076,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4085,19 +4102,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4146,7 +4163,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4161,19 +4178,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4181,10 +4198,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4207,16 +4224,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4266,7 +4283,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4287,13 +4304,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4301,10 +4318,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4327,17 +4344,17 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4386,7 +4403,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4401,19 +4418,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4421,10 +4438,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4447,19 +4464,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4496,19 +4513,17 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4517,7 +4532,7 @@
         <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
@@ -4526,29 +4541,31 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4566,22 +4583,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4606,13 +4623,11 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4630,7 +4645,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4639,7 +4654,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4648,38 +4663,38 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>135</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4694,16 +4709,16 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4728,13 +4743,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4752,16 +4767,16 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI25" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4770,31 +4785,31 @@
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4813,19 +4828,19 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>303</v>
+        <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4850,13 +4865,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4874,7 +4887,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4892,27 +4905,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4923,7 +4936,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -4935,18 +4948,20 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>190</v>
+        <v>304</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -4970,13 +4985,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4994,13 +5009,13 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5012,27 +5027,27 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5058,17 +5073,15 @@
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5092,13 +5105,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>205</v>
+        <v>315</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5116,7 +5129,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5134,27 +5147,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5177,18 +5190,20 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>330</v>
+        <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5212,13 +5227,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5236,7 +5251,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5254,27 +5269,27 @@
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5297,16 +5312,16 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5356,7 +5371,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5374,27 +5389,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5405,7 +5420,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5417,20 +5432,18 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5478,45 +5491,45 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5527,7 +5540,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5539,16 +5552,20 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5596,19 +5613,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5617,10 +5634,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5631,21 +5648,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5657,17 +5674,15 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>139</v>
+        <v>360</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5716,19 +5731,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5740,7 +5755,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5751,14 +5766,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>366</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5771,26 +5786,24 @@
         <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O34" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5838,7 +5851,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5862,7 +5875,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>135</v>
+        <v>363</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5873,42 +5886,46 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>371</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -5956,19 +5973,19 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -5977,10 +5994,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>376</v>
+        <v>135</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -5991,10 +6008,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6017,13 +6034,13 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6074,7 +6091,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6083,7 +6100,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6095,10 +6112,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6109,10 +6126,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6135,20 +6152,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>190</v>
+        <v>373</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6172,13 +6185,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6196,7 +6209,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6205,7 +6218,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6214,13 +6227,13 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6231,10 +6244,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6245,7 +6258,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6260,16 +6273,16 @@
         <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6294,13 +6307,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>205</v>
+        <v>116</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6318,13 +6331,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6336,13 +6349,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6353,10 +6366,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6367,7 +6380,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6379,17 +6392,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>398</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6414,13 +6429,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6438,13 +6453,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6456,13 +6471,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6473,10 +6488,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6499,16 +6514,18 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6556,7 +6573,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6577,10 +6594,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6591,10 +6608,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6605,7 +6622,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6614,20 +6631,18 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6676,13 +6691,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -6697,10 +6712,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>412</v>
+        <v>377</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6711,10 +6726,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6737,16 +6752,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6796,7 +6811,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6817,10 +6832,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6831,10 +6846,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6857,20 +6872,18 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6918,7 +6931,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6939,10 +6952,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6953,10 +6966,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6967,7 +6980,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -6976,19 +6989,23 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>358</v>
+        <v>423</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7036,19 +7053,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>360</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7057,10 +7074,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>361</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7071,21 +7088,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7097,17 +7114,15 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>139</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7156,19 +7171,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7180,7 +7195,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7191,14 +7206,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>366</v>
+        <v>137</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7211,26 +7226,24 @@
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>367</v>
+        <v>139</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7278,7 +7291,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7302,7 +7315,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>135</v>
+        <v>363</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7313,45 +7326,45 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>431</v>
+        <v>369</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>432</v>
+        <v>370</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>433</v>
+        <v>141</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>204</v>
+        <v>147</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7376,13 +7389,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7400,34 +7413,34 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>430</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>211</v>
+        <v>135</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7435,10 +7448,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7446,7 +7459,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>92</v>
@@ -7461,19 +7474,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>272</v>
+        <v>434</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>274</v>
+        <v>204</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7498,13 +7511,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7522,10 +7535,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>92</v>
@@ -7543,16 +7556,16 @@
         <v>438</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>277</v>
+        <v>209</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>278</v>
+        <v>210</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
@@ -7580,22 +7593,22 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>190</v>
+        <v>269</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7620,13 +7633,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7653,7 +7666,7 @@
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -7662,19 +7675,19 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>135</v>
+        <v>278</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50">
@@ -7686,14 +7699,14 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7708,16 +7721,16 @@
         <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>292</v>
+        <v>444</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>293</v>
+        <v>445</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>294</v>
+        <v>446</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7742,13 +7755,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7772,10 +7785,10 @@
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>104</v>
@@ -7784,31 +7797,31 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7827,19 +7840,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>294</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
+        <v>295</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>352</v>
+        <v>297</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7864,13 +7877,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7888,7 +7901,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7906,18 +7919,140 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
+      <c r="P52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T11:26:43+00:00</t>
+    <t>2025-01-29T08:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -622,10 +622,10 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-ips-laboratory-pathology-category</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -651,9 +651,6 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-ips-laboratory-pathology-codes</t>
@@ -1760,7 +1757,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="87.55859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="90.28515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3533,11 +3530,9 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>195</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>196</v>
       </c>
@@ -3655,11 +3650,11 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3692,30 +3687,30 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3738,19 +3733,19 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3799,7 +3794,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3814,19 +3809,19 @@
         <v>104</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3834,10 +3829,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3860,16 +3855,16 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3919,7 +3914,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3940,13 +3935,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3954,14 +3949,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3980,19 +3975,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4041,7 +4036,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4056,19 +4051,19 @@
         <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4076,14 +4071,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4102,19 +4097,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4163,7 +4158,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4178,19 +4173,19 @@
         <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4198,10 +4193,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4224,16 +4219,16 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4283,7 +4278,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4304,13 +4299,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4318,10 +4313,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4344,17 +4339,17 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4403,7 +4398,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4418,19 +4413,19 @@
         <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4438,10 +4433,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4464,19 +4459,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4513,17 +4508,17 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4532,7 +4527,7 @@
         <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>104</v>
@@ -4541,30 +4536,30 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>82</v>
@@ -4589,16 +4584,16 @@
         <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4623,7 +4618,7 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
@@ -4645,7 +4640,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4654,7 +4649,7 @@
         <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4663,27 +4658,27 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4709,16 +4704,16 @@
         <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4743,14 +4738,14 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4767,7 +4762,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4776,7 +4771,7 @@
         <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4791,7 +4786,7 @@
         <v>135</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -4802,14 +4797,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4831,16 +4826,16 @@
         <v>190</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4865,11 +4860,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4887,7 +4882,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4905,27 +4900,27 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4948,19 +4943,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5009,7 +5004,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5030,10 +5025,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5044,10 +5039,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5073,13 +5068,13 @@
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5105,14 +5100,14 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5129,7 +5124,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5147,27 +5142,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5193,16 +5188,16 @@
         <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5227,14 +5222,14 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5251,7 +5246,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5272,10 +5267,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5286,10 +5281,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5297,7 +5292,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>92</v>
@@ -5312,16 +5307,16 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5371,7 +5366,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5389,27 +5384,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5432,16 +5427,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5491,7 +5486,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5509,27 +5504,27 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5552,19 +5547,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5613,7 +5608,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5625,19 +5620,19 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5648,10 +5643,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5674,13 +5669,13 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5731,7 +5726,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5755,7 +5750,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5766,10 +5761,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5798,7 +5793,7 @@
         <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>141</v>
@@ -5851,7 +5846,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5875,7 +5870,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5886,14 +5881,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5915,10 +5910,10 @@
         <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>141</v>
@@ -5973,7 +5968,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6008,10 +6003,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6034,13 +6029,13 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6091,7 +6086,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6100,7 +6095,7 @@
         <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6112,10 +6107,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6126,10 +6121,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6152,13 +6147,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6209,7 +6204,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6218,7 +6213,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6230,10 +6225,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6244,10 +6239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6273,16 +6268,16 @@
         <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6310,11 +6305,11 @@
         <v>116</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6331,7 +6326,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6349,13 +6344,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6366,10 +6361,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6395,16 +6390,16 @@
         <v>190</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6429,14 +6424,14 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6453,7 +6448,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6471,13 +6466,13 @@
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6488,10 +6483,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6514,17 +6509,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6573,7 +6568,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6597,7 +6592,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6608,10 +6603,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6634,13 +6629,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6691,7 +6686,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6712,10 +6707,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6726,10 +6721,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6752,16 +6747,16 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6811,7 +6806,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6832,10 +6827,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6846,10 +6841,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6872,16 +6867,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6931,7 +6926,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6952,10 +6947,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6966,10 +6961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6992,19 +6987,19 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7053,7 +7048,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7074,10 +7069,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7088,10 +7083,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7114,13 +7109,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7171,7 +7166,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7195,7 +7190,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7206,10 +7201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7238,7 +7233,7 @@
         <v>139</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>141</v>
@@ -7291,7 +7286,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7315,7 +7310,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7326,14 +7321,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7355,10 +7350,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -7413,7 +7408,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7448,10 +7443,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7477,13 +7472,13 @@
         <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>204</v>
@@ -7511,14 +7506,14 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7535,7 +7530,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>92</v>
@@ -7553,16 +7548,16 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7570,10 +7565,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7596,19 +7591,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7657,7 +7652,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7675,27 +7670,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7721,16 +7716,16 @@
         <v>190</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7755,14 +7750,14 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7779,7 +7774,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7788,7 +7783,7 @@
         <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>104</v>
@@ -7803,7 +7798,7 @@
         <v>135</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7814,14 +7809,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7843,16 +7838,16 @@
         <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7877,14 +7872,14 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7901,7 +7896,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7919,27 +7914,27 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>302</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7965,16 +7960,16 @@
         <v>83</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="N52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8023,7 +8018,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8044,10 +8039,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T08:49:29+00:00</t>
+    <t>2025-01-29T12:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T12:34:29+00:00</t>
+    <t>2025-02-03T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>92</v>
